--- a/artfynd/A 13211-2026 artfynd.xlsx
+++ b/artfynd/A 13211-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126578656</v>
+        <v>126578680</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578569</v>
+        <v>578620</v>
       </c>
       <c r="R2" t="n">
-        <v>7153745</v>
+        <v>7153807</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack under 5 år gammalt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126578680</v>
+        <v>126578668</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578620</v>
+        <v>578618</v>
       </c>
       <c r="R3" t="n">
-        <v>7153807</v>
+        <v>7153783</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,7 +872,7 @@
         <v>126578634</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,6 +968,108 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126578656</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tallmyran, Tallmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>578569</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7153745</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack under 5 år gammalt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl Wiking</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl Wiking</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
